--- a/artfynd/A 34144-2026 artfynd.xlsx
+++ b/artfynd/A 34144-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136102014</v>
       </c>
       <c r="B2" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136102115</v>
       </c>
       <c r="B3" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>136102455</v>
       </c>
       <c r="B6" t="n">
-        <v>80508</v>
+        <v>80509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34144-2026 artfynd.xlsx
+++ b/artfynd/A 34144-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136102014</v>
       </c>
       <c r="B2" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34144-2026 artfynd.xlsx
+++ b/artfynd/A 34144-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136102014</v>
       </c>
       <c r="B2" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136102115</v>
       </c>
       <c r="B3" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136102493</v>
       </c>
       <c r="B4" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136101992</v>
       </c>
       <c r="B5" t="n">
-        <v>57160</v>
+        <v>57161</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>136102455</v>
       </c>
       <c r="B6" t="n">
-        <v>80509</v>
+        <v>80510</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34144-2026 artfynd.xlsx
+++ b/artfynd/A 34144-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136102014</v>
       </c>
       <c r="B2" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136102115</v>
       </c>
       <c r="B3" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136102493</v>
       </c>
       <c r="B4" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136101992</v>
       </c>
       <c r="B5" t="n">
-        <v>57161</v>
+        <v>57165</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>136102455</v>
       </c>
       <c r="B6" t="n">
-        <v>80510</v>
+        <v>80514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34144-2026 artfynd.xlsx
+++ b/artfynd/A 34144-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136102014</v>
       </c>
       <c r="B2" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136102115</v>
       </c>
       <c r="B3" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136102493</v>
       </c>
       <c r="B4" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136101992</v>
       </c>
       <c r="B5" t="n">
-        <v>57165</v>
+        <v>57166</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>136102455</v>
       </c>
       <c r="B6" t="n">
-        <v>80514</v>
+        <v>80515</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34144-2026 artfynd.xlsx
+++ b/artfynd/A 34144-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136102014</v>
       </c>
       <c r="B2" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136102115</v>
       </c>
       <c r="B3" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>136102455</v>
       </c>
       <c r="B6" t="n">
-        <v>80515</v>
+        <v>80519</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34144-2026 artfynd.xlsx
+++ b/artfynd/A 34144-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136102014</v>
       </c>
       <c r="B2" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136102115</v>
       </c>
       <c r="B3" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136102493</v>
       </c>
       <c r="B4" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136101992</v>
       </c>
       <c r="B5" t="n">
-        <v>57166</v>
+        <v>57171</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>136102455</v>
       </c>
       <c r="B6" t="n">
-        <v>80519</v>
+        <v>80525</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34144-2026 artfynd.xlsx
+++ b/artfynd/A 34144-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136102014</v>
       </c>
       <c r="B2" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 34144-2026 artfynd.xlsx
+++ b/artfynd/A 34144-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136102014</v>
       </c>
       <c r="B2" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136102115</v>
       </c>
       <c r="B3" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136102493</v>
       </c>
       <c r="B4" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136101992</v>
       </c>
       <c r="B5" t="n">
-        <v>57171</v>
+        <v>57184</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>136102455</v>
       </c>
       <c r="B6" t="n">
-        <v>80525</v>
+        <v>80538</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34144-2026 artfynd.xlsx
+++ b/artfynd/A 34144-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136102014</v>
       </c>
       <c r="B2" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136102115</v>
       </c>
       <c r="B3" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>136102455</v>
       </c>
       <c r="B6" t="n">
-        <v>80538</v>
+        <v>80539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
